--- a/Overpotnital/Air/BOL/Edited/CN BM air_edited.xlsx
+++ b/Overpotnital/Air/BOL/Edited/CN BM air_edited.xlsx
@@ -612,10 +612,10 @@
         <f>A4*B4</f>
         <v/>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F4" s="0">
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="S4" s="0" t="n">
-        <v>-0.513</v>
+        <v>-0.517</v>
       </c>
       <c r="V4" s="0" t="n">
         <v>-6</v>
@@ -684,10 +684,10 @@
         <f>A5*B5</f>
         <v/>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F5" s="0">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="S5" s="0" t="n">
-        <v>-0.0351</v>
+        <v>-0.0358</v>
       </c>
       <c r="V5" s="0" t="n">
         <v>-5.9</v>
@@ -756,10 +756,10 @@
         <f>A6*B6</f>
         <v/>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F6" s="0">
@@ -820,10 +820,10 @@
         <f>A7*B7</f>
         <v/>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F7" s="0">
@@ -884,10 +884,10 @@
         <f>A8*B8</f>
         <v/>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F8" s="0">
@@ -948,10 +948,10 @@
         <f>A9*B9</f>
         <v/>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F9" s="0">
@@ -1012,10 +1012,10 @@
         <f>A10*B10</f>
         <v/>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F10" s="0">
@@ -1076,10 +1076,10 @@
         <f>A11*B11</f>
         <v/>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F11" s="0">
@@ -1140,10 +1140,10 @@
         <f>A12*B12</f>
         <v/>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F12" s="0">
@@ -1204,10 +1204,10 @@
         <f>A13*B13</f>
         <v/>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F13" s="0">
@@ -1268,10 +1268,10 @@
         <f>A14*B14</f>
         <v/>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F14" s="0">
@@ -1332,10 +1332,10 @@
         <f>A15*B15</f>
         <v/>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F15" s="0">
@@ -1396,10 +1396,10 @@
         <f>A16*B16</f>
         <v/>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F16" s="0">
@@ -1460,10 +1460,10 @@
         <f>A17*B17</f>
         <v/>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F17" s="0">
@@ -1524,10 +1524,10 @@
         <f>A18*B18</f>
         <v/>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F18" s="0">
@@ -1588,10 +1588,10 @@
         <f>A19*B19</f>
         <v/>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F19" s="0">
@@ -1652,10 +1652,10 @@
         <f>A20*B20</f>
         <v/>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F20" s="0">
@@ -1716,10 +1716,10 @@
         <f>A21*B21</f>
         <v/>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F21" s="0">
@@ -1780,10 +1780,10 @@
         <f>A22*B22</f>
         <v/>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F22" s="0">
@@ -1844,10 +1844,10 @@
         <f>A23*B23</f>
         <v/>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F23" s="0">
@@ -1908,10 +1908,10 @@
         <f>A24*B24</f>
         <v/>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F24" s="0">
@@ -1972,10 +1972,10 @@
         <f>A25*B25</f>
         <v/>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F25" s="0">
@@ -2036,10 +2036,10 @@
         <f>A26*B26</f>
         <v/>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F26" s="0">
@@ -2100,10 +2100,10 @@
         <f>A27*B27</f>
         <v/>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F27" s="0">
@@ -2164,10 +2164,10 @@
         <f>A28*B28</f>
         <v/>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F28" s="0">
@@ -2228,10 +2228,10 @@
         <f>A29*B29</f>
         <v/>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F29" s="0">
@@ -2292,10 +2292,10 @@
         <f>A30*B30</f>
         <v/>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F30" s="0">
@@ -2356,10 +2356,10 @@
         <f>A31*B31</f>
         <v/>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F31" s="0">
@@ -2420,10 +2420,10 @@
         <f>A32*B32</f>
         <v/>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F32" s="0">
@@ -2484,10 +2484,10 @@
         <f>A33*B33</f>
         <v/>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F33" s="0">
@@ -2548,10 +2548,10 @@
         <f>A34*B34</f>
         <v/>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F34" s="0">
@@ -2612,10 +2612,10 @@
         <f>A35*B35</f>
         <v/>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F35" s="0">
@@ -2676,10 +2676,10 @@
         <f>A36*B36</f>
         <v/>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F36" s="0">
@@ -2740,10 +2740,10 @@
         <f>A37*B37</f>
         <v/>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F37" s="0">
@@ -2804,10 +2804,10 @@
         <f>A38*B38</f>
         <v/>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F38" s="0">
@@ -2868,10 +2868,10 @@
         <f>A39*B39</f>
         <v/>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F39" s="0">
@@ -2932,10 +2932,10 @@
         <f>A40*B40</f>
         <v/>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F40" s="0">
@@ -2996,10 +2996,10 @@
         <f>A41*B41</f>
         <v/>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F41" s="0">
@@ -3060,10 +3060,10 @@
         <f>A42*B42</f>
         <v/>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F42" s="0">
@@ -3124,10 +3124,10 @@
         <f>A43*B43</f>
         <v/>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F43" s="0">
@@ -3188,10 +3188,10 @@
         <f>A44*B44</f>
         <v/>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E44" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F44" s="0">
@@ -3252,10 +3252,10 @@
         <f>A45*B45</f>
         <v/>
       </c>
-      <c r="D45" t="n">
+      <c r="D45" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F45" s="0">
@@ -3316,10 +3316,10 @@
         <f>A46*B46</f>
         <v/>
       </c>
-      <c r="D46" t="n">
+      <c r="D46" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E46" t="n">
+      <c r="E46" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F46" s="0">
@@ -3380,10 +3380,10 @@
         <f>A47*B47</f>
         <v/>
       </c>
-      <c r="D47" t="n">
+      <c r="D47" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E47" t="n">
+      <c r="E47" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F47" s="0">
@@ -3444,10 +3444,10 @@
         <f>A48*B48</f>
         <v/>
       </c>
-      <c r="D48" t="n">
+      <c r="D48" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E48" t="n">
+      <c r="E48" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F48" s="0">
@@ -3508,10 +3508,10 @@
         <f>A49*B49</f>
         <v/>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E49" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F49" s="0">
@@ -3572,10 +3572,10 @@
         <f>A50*B50</f>
         <v/>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E50" t="n">
+      <c r="E50" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F50" s="0">
@@ -3636,10 +3636,10 @@
         <f>A51*B51</f>
         <v/>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E51" t="n">
+      <c r="E51" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F51" s="0">
@@ -3700,10 +3700,10 @@
         <f>A52*B52</f>
         <v/>
       </c>
-      <c r="D52" t="n">
+      <c r="D52" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E52" t="n">
+      <c r="E52" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F52" s="0">
@@ -3764,10 +3764,10 @@
         <f>A53*B53</f>
         <v/>
       </c>
-      <c r="D53" t="n">
+      <c r="D53" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E53" t="n">
+      <c r="E53" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F53" s="0">
@@ -3828,10 +3828,10 @@
         <f>A54*B54</f>
         <v/>
       </c>
-      <c r="D54" t="n">
+      <c r="D54" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E54" t="n">
+      <c r="E54" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F54" s="0">
@@ -3892,10 +3892,10 @@
         <f>A55*B55</f>
         <v/>
       </c>
-      <c r="D55" t="n">
+      <c r="D55" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E55" t="n">
+      <c r="E55" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F55" s="0">
@@ -3956,10 +3956,10 @@
         <f>A56*B56</f>
         <v/>
       </c>
-      <c r="D56" t="n">
+      <c r="D56" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E56" t="n">
+      <c r="E56" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F56" s="0">
@@ -4020,10 +4020,10 @@
         <f>A57*B57</f>
         <v/>
       </c>
-      <c r="D57" t="n">
+      <c r="D57" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E57" t="n">
+      <c r="E57" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F57" s="0">
@@ -4084,10 +4084,10 @@
         <f>A58*B58</f>
         <v/>
       </c>
-      <c r="D58" t="n">
+      <c r="D58" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E58" t="n">
+      <c r="E58" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F58" s="0">
@@ -4148,10 +4148,10 @@
         <f>A59*B59</f>
         <v/>
       </c>
-      <c r="D59" t="n">
+      <c r="D59" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E59" t="n">
+      <c r="E59" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F59" s="0">
@@ -4212,10 +4212,10 @@
         <f>A60*B60</f>
         <v/>
       </c>
-      <c r="D60" t="n">
+      <c r="D60" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E60" t="n">
+      <c r="E60" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F60" s="0">
@@ -4276,10 +4276,10 @@
         <f>A61*B61</f>
         <v/>
       </c>
-      <c r="D61" t="n">
+      <c r="D61" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E61" t="n">
+      <c r="E61" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F61" s="0">
@@ -4340,10 +4340,10 @@
         <f>A62*B62</f>
         <v/>
       </c>
-      <c r="D62" t="n">
+      <c r="D62" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E62" t="n">
+      <c r="E62" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F62" s="0">
@@ -4404,10 +4404,10 @@
         <f>A63*B63</f>
         <v/>
       </c>
-      <c r="D63" t="n">
+      <c r="D63" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E63" t="n">
+      <c r="E63" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F63" s="0">
@@ -4468,10 +4468,10 @@
         <f>A64*B64</f>
         <v/>
       </c>
-      <c r="D64" t="n">
+      <c r="D64" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E64" t="n">
+      <c r="E64" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F64" s="0">
@@ -4532,10 +4532,10 @@
         <f>A65*B65</f>
         <v/>
       </c>
-      <c r="D65" t="n">
+      <c r="D65" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E65" t="n">
+      <c r="E65" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F65" s="0">
@@ -4596,10 +4596,10 @@
         <f>A66*B66</f>
         <v/>
       </c>
-      <c r="D66" t="n">
+      <c r="D66" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E66" t="n">
+      <c r="E66" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F66" s="0">
@@ -4660,10 +4660,10 @@
         <f>A67*B67</f>
         <v/>
       </c>
-      <c r="D67" t="n">
+      <c r="D67" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E67" t="n">
+      <c r="E67" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F67" s="0">
@@ -4724,10 +4724,10 @@
         <f>A68*B68</f>
         <v/>
       </c>
-      <c r="D68" t="n">
+      <c r="D68" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E68" t="n">
+      <c r="E68" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F68" s="0">
@@ -4788,10 +4788,10 @@
         <f>A69*B69</f>
         <v/>
       </c>
-      <c r="D69" t="n">
+      <c r="D69" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E69" t="n">
+      <c r="E69" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F69" s="0">
@@ -4852,10 +4852,10 @@
         <f>A70*B70</f>
         <v/>
       </c>
-      <c r="D70" t="n">
+      <c r="D70" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E70" t="n">
+      <c r="E70" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F70" s="0">
@@ -4916,10 +4916,10 @@
         <f>A71*B71</f>
         <v/>
       </c>
-      <c r="D71" t="n">
+      <c r="D71" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E71" t="n">
+      <c r="E71" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F71" s="0">
@@ -4980,10 +4980,10 @@
         <f>A72*B72</f>
         <v/>
       </c>
-      <c r="D72" t="n">
+      <c r="D72" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E72" t="n">
+      <c r="E72" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F72" s="0">
@@ -5044,10 +5044,10 @@
         <f>A73*B73</f>
         <v/>
       </c>
-      <c r="D73" t="n">
+      <c r="D73" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E73" t="n">
+      <c r="E73" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F73" s="0">
@@ -5108,10 +5108,10 @@
         <f>A74*B74</f>
         <v/>
       </c>
-      <c r="D74" t="n">
+      <c r="D74" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E74" t="n">
+      <c r="E74" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F74" s="0">
@@ -5172,10 +5172,10 @@
         <f>A75*B75</f>
         <v/>
       </c>
-      <c r="D75" t="n">
+      <c r="D75" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E75" t="n">
+      <c r="E75" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F75" s="0">
@@ -5236,10 +5236,10 @@
         <f>A76*B76</f>
         <v/>
       </c>
-      <c r="D76" t="n">
+      <c r="D76" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E76" t="n">
+      <c r="E76" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F76" s="0">
@@ -5300,10 +5300,10 @@
         <f>A77*B77</f>
         <v/>
       </c>
-      <c r="D77" t="n">
+      <c r="D77" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E77" t="n">
+      <c r="E77" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F77" s="0">
@@ -5364,10 +5364,10 @@
         <f>A78*B78</f>
         <v/>
       </c>
-      <c r="D78" t="n">
+      <c r="D78" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E78" t="n">
+      <c r="E78" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F78" s="0">
@@ -5428,10 +5428,10 @@
         <f>A79*B79</f>
         <v/>
       </c>
-      <c r="D79" t="n">
+      <c r="D79" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E79" t="n">
+      <c r="E79" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F79" s="0">
@@ -5492,10 +5492,10 @@
         <f>A80*B80</f>
         <v/>
       </c>
-      <c r="D80" t="n">
+      <c r="D80" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E80" t="n">
+      <c r="E80" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F80" s="0">
@@ -5556,10 +5556,10 @@
         <f>A81*B81</f>
         <v/>
       </c>
-      <c r="D81" t="n">
+      <c r="D81" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E81" t="n">
+      <c r="E81" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F81" s="0">
@@ -5620,10 +5620,10 @@
         <f>A82*B82</f>
         <v/>
       </c>
-      <c r="D82" t="n">
+      <c r="D82" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E82" t="n">
+      <c r="E82" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F82" s="0">
@@ -5684,10 +5684,10 @@
         <f>A83*B83</f>
         <v/>
       </c>
-      <c r="D83" t="n">
+      <c r="D83" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E83" t="n">
+      <c r="E83" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F83" s="0">
@@ -5748,10 +5748,10 @@
         <f>A84*B84</f>
         <v/>
       </c>
-      <c r="D84" t="n">
+      <c r="D84" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E84" t="n">
+      <c r="E84" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F84" s="0">
@@ -5812,10 +5812,10 @@
         <f>A85*B85</f>
         <v/>
       </c>
-      <c r="D85" t="n">
+      <c r="D85" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E85" t="n">
+      <c r="E85" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F85" s="0">
@@ -5876,10 +5876,10 @@
         <f>A86*B86</f>
         <v/>
       </c>
-      <c r="D86" t="n">
+      <c r="D86" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E86" t="n">
+      <c r="E86" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F86" s="0">
@@ -5940,10 +5940,10 @@
         <f>A87*B87</f>
         <v/>
       </c>
-      <c r="D87" t="n">
+      <c r="D87" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E87" t="n">
+      <c r="E87" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F87" s="0">
@@ -6004,10 +6004,10 @@
         <f>A88*B88</f>
         <v/>
       </c>
-      <c r="D88" t="n">
+      <c r="D88" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E88" t="n">
+      <c r="E88" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F88" s="0">
@@ -6068,10 +6068,10 @@
         <f>A89*B89</f>
         <v/>
       </c>
-      <c r="D89" t="n">
+      <c r="D89" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E89" t="n">
+      <c r="E89" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F89" s="0">
@@ -6132,10 +6132,10 @@
         <f>A90*B90</f>
         <v/>
       </c>
-      <c r="D90" t="n">
+      <c r="D90" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E90" t="n">
+      <c r="E90" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F90" s="0">
@@ -6196,10 +6196,10 @@
         <f>A91*B91</f>
         <v/>
       </c>
-      <c r="D91" t="n">
+      <c r="D91" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E91" t="n">
+      <c r="E91" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F91" s="0">
@@ -6260,10 +6260,10 @@
         <f>A92*B92</f>
         <v/>
       </c>
-      <c r="D92" t="n">
+      <c r="D92" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E92" t="n">
+      <c r="E92" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F92" s="0">
@@ -6324,10 +6324,10 @@
         <f>A93*B93</f>
         <v/>
       </c>
-      <c r="D93" t="n">
+      <c r="D93" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E93" t="n">
+      <c r="E93" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F93" s="0">
@@ -6388,10 +6388,10 @@
         <f>A94*B94</f>
         <v/>
       </c>
-      <c r="D94" t="n">
+      <c r="D94" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E94" t="n">
+      <c r="E94" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F94" s="0">
@@ -6452,10 +6452,10 @@
         <f>A95*B95</f>
         <v/>
       </c>
-      <c r="D95" t="n">
+      <c r="D95" s="0" t="n">
         <v>0.021</v>
       </c>
-      <c r="E95" t="n">
+      <c r="E95" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F95" s="0">
@@ -11805,7 +11805,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="n">
+      <c r="A134" s="0" t="n">
         <v>1388.53066</v>
       </c>
       <c r="B134" s="0" t="n">
@@ -11821,7 +11821,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="n">
+      <c r="A135" s="0" t="n">
         <v>1398.81612</v>
       </c>
       <c r="B135" s="0" t="n">
@@ -11837,7 +11837,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="n">
+      <c r="A136" s="0" t="n">
         <v>1408.89794</v>
       </c>
       <c r="B136" s="0" t="n">
@@ -11853,7 +11853,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="n">
+      <c r="A137" s="0" t="n">
         <v>1419.08174</v>
       </c>
       <c r="B137" s="0" t="n">
@@ -11869,7 +11869,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="n">
+      <c r="A138" s="0" t="n">
         <v>1429.36708</v>
       </c>
       <c r="B138" s="0" t="n">
@@ -11885,7 +11885,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="n">
+      <c r="A139" s="0" t="n">
         <v>1440.05996</v>
       </c>
       <c r="B139" s="0" t="n">
@@ -11901,7 +11901,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="n">
+      <c r="A140" s="0" t="n">
         <v>1450.1418</v>
       </c>
       <c r="B140" s="0" t="n">
@@ -11917,7 +11917,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="n">
+      <c r="A141" s="0" t="n">
         <v>1452.99336</v>
       </c>
       <c r="B141" s="0" t="n">
